--- a/Phân loại.xlsx
+++ b/Phân loại.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F602DCC-4472-4183-9F2B-980F761E9A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E5830A-8E47-42D4-9FF0-02B59F360A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38A6C064-8983-4FF8-9C29-8BEDF747C796}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="155">
   <si>
     <t>Lớp</t>
   </si>
@@ -76,9 +75,6 @@
   </si>
   <si>
     <t>Dùng tính đơn điệu để so sánh giá trị hoặc giải bất phương trình</t>
-  </si>
-  <si>
-    <t>Kiểm tra nhiều tính chất của một hàm số cho bởi công thức</t>
   </si>
   <si>
     <t>Tìm giá trị lớn nhất, nhỏ nhất của hàm đa thức hoặc phân thức trên đoạn</t>
@@ -602,7 +598,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -940,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7BC53D4-DA32-46F8-8217-5D3B03E35241}">
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C147"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="76.5" customWidth="1"/>
@@ -1414,10 +1410,10 @@
         <v>12</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1425,7 +1421,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>47</v>
@@ -1436,7 +1432,7 @@
         <v>12</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>48</v>
@@ -1447,7 +1443,7 @@
         <v>12</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>49</v>
@@ -1458,7 +1454,7 @@
         <v>12</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>50</v>
@@ -1469,7 +1465,7 @@
         <v>12</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>51</v>
@@ -1480,7 +1476,7 @@
         <v>12</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>52</v>
@@ -1491,7 +1487,7 @@
         <v>12</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>53</v>
@@ -1502,7 +1498,7 @@
         <v>12</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>54</v>
@@ -1513,7 +1509,7 @@
         <v>12</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>55</v>
@@ -1524,7 +1520,7 @@
         <v>12</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>56</v>
@@ -1535,7 +1531,7 @@
         <v>12</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>57</v>
@@ -1546,7 +1542,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>58</v>
@@ -1557,7 +1553,7 @@
         <v>12</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>59</v>
@@ -1568,7 +1564,7 @@
         <v>12</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>60</v>
@@ -1579,7 +1575,7 @@
         <v>12</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>61</v>
@@ -1590,7 +1586,7 @@
         <v>12</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>62</v>
@@ -1601,7 +1597,7 @@
         <v>12</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>63</v>
@@ -1612,7 +1608,7 @@
         <v>12</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>64</v>
@@ -1623,7 +1619,7 @@
         <v>12</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>65</v>
@@ -1634,7 +1630,7 @@
         <v>12</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>66</v>
@@ -1645,10 +1641,10 @@
         <v>12</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1656,7 +1652,7 @@
         <v>12</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>69</v>
@@ -1667,7 +1663,7 @@
         <v>12</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>70</v>
@@ -1678,29 +1674,29 @@
         <v>12</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>12</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>12</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>73</v>
@@ -1711,7 +1707,7 @@
         <v>12</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>74</v>
@@ -1722,7 +1718,7 @@
         <v>12</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>75</v>
@@ -1733,7 +1729,7 @@
         <v>12</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>76</v>
@@ -1744,7 +1740,7 @@
         <v>12</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>77</v>
@@ -1755,7 +1751,7 @@
         <v>12</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>78</v>
@@ -1766,10 +1762,10 @@
         <v>12</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1777,7 +1773,7 @@
         <v>12</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>81</v>
@@ -1788,7 +1784,7 @@
         <v>12</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>82</v>
@@ -1799,7 +1795,7 @@
         <v>12</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>83</v>
@@ -1810,7 +1806,7 @@
         <v>12</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>84</v>
@@ -1821,7 +1817,7 @@
         <v>12</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>85</v>
@@ -1832,7 +1828,7 @@
         <v>12</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>86</v>
@@ -1843,7 +1839,7 @@
         <v>12</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>87</v>
@@ -1854,7 +1850,7 @@
         <v>12</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>88</v>
@@ -1865,29 +1861,29 @@
         <v>12</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>12</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>12</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>91</v>
@@ -1898,7 +1894,7 @@
         <v>12</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>92</v>
@@ -1909,7 +1905,7 @@
         <v>12</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>93</v>
@@ -1920,7 +1916,7 @@
         <v>12</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>94</v>
@@ -1931,7 +1927,7 @@
         <v>12</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>95</v>
@@ -1942,7 +1938,7 @@
         <v>12</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>96</v>
@@ -1953,7 +1949,7 @@
         <v>12</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>97</v>
@@ -1964,7 +1960,7 @@
         <v>12</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>98</v>
@@ -1975,7 +1971,7 @@
         <v>12</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>99</v>
@@ -1986,7 +1982,7 @@
         <v>12</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>100</v>
@@ -1997,7 +1993,7 @@
         <v>12</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>101</v>
@@ -2008,10 +2004,10 @@
         <v>12</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2019,7 +2015,7 @@
         <v>12</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>104</v>
@@ -2030,29 +2026,29 @@
         <v>12</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>12</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>12</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>107</v>
@@ -2063,7 +2059,7 @@
         <v>12</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>108</v>
@@ -2074,10 +2070,10 @@
         <v>12</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2085,7 +2081,7 @@
         <v>12</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>111</v>
@@ -2096,29 +2092,29 @@
         <v>12</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>12</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>12</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>114</v>
@@ -2129,7 +2125,7 @@
         <v>12</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>115</v>
@@ -2140,7 +2136,7 @@
         <v>12</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>116</v>
@@ -2151,10 +2147,10 @@
         <v>12</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2162,10 +2158,10 @@
         <v>12</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2173,7 +2169,7 @@
         <v>12</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>118</v>
@@ -2184,7 +2180,7 @@
         <v>12</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>119</v>
@@ -2195,7 +2191,7 @@
         <v>12</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>120</v>
@@ -2206,7 +2202,7 @@
         <v>12</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>121</v>
@@ -2217,7 +2213,7 @@
         <v>12</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>122</v>
@@ -2228,7 +2224,7 @@
         <v>12</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>123</v>
@@ -2239,7 +2235,7 @@
         <v>12</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>124</v>
@@ -2250,7 +2246,7 @@
         <v>12</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -2261,7 +2257,7 @@
         <v>12</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>126</v>
@@ -2272,10 +2268,10 @@
         <v>12</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2283,10 +2279,10 @@
         <v>12</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2294,7 +2290,7 @@
         <v>12</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>128</v>
@@ -2305,7 +2301,7 @@
         <v>12</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>129</v>
@@ -2316,7 +2312,7 @@
         <v>12</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>130</v>
@@ -2327,7 +2323,7 @@
         <v>12</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>131</v>
@@ -2338,7 +2334,7 @@
         <v>12</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>132</v>
@@ -2349,7 +2345,7 @@
         <v>12</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>133</v>
@@ -2360,10 +2356,10 @@
         <v>12</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2371,7 +2367,7 @@
         <v>12</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>136</v>
@@ -2382,7 +2378,7 @@
         <v>12</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>137</v>
@@ -2393,7 +2389,7 @@
         <v>12</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>138</v>
@@ -2404,7 +2400,7 @@
         <v>12</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>139</v>
@@ -2415,10 +2411,10 @@
         <v>12</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2426,7 +2422,7 @@
         <v>12</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>142</v>
@@ -2437,7 +2433,7 @@
         <v>12</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>143</v>
@@ -2448,7 +2444,7 @@
         <v>12</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>144</v>
@@ -2459,21 +2455,21 @@
         <v>12</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C138" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3">
+        <v>12</v>
+      </c>
+      <c r="B139" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="2">
-        <v>12</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>141</v>
+      <c r="C139" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -2481,9 +2477,9 @@
         <v>12</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C140" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2492,7 +2488,7 @@
         <v>12</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>148</v>
@@ -2503,7 +2499,7 @@
         <v>12</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>149</v>
@@ -2514,7 +2510,7 @@
         <v>12</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>150</v>
@@ -2525,7 +2521,7 @@
         <v>12</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>151</v>
@@ -2536,7 +2532,7 @@
         <v>12</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>152</v>
@@ -2547,7 +2543,7 @@
         <v>12</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>153</v>
@@ -2558,21 +2554,10 @@
         <v>12</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="3">
-        <v>12</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Phân loại.xlsx
+++ b/Phân loại.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E5830A-8E47-42D4-9FF0-02B59F360A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F90264-7179-46E7-9376-D8B14168AC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38A6C064-8983-4FF8-9C29-8BEDF747C796}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{38A6C064-8983-4FF8-9C29-8BEDF747C796}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="272">
   <si>
     <t>Lớp</t>
   </si>
@@ -504,6 +504,357 @@
   </si>
   <si>
     <t>Đạo hàm</t>
+  </si>
+  <si>
+    <t>Chương 1. Hàm số lượng giác và phương trình lượng giác</t>
+  </si>
+  <si>
+    <t>Tính hoặc rút gọn giá trị lượng giác của một góc</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế dùng giá trị lượng giác</t>
+  </si>
+  <si>
+    <t>Dùng công thức cộng hoặc công thức nhân đôi để tính, rút gọn</t>
+  </si>
+  <si>
+    <t>Biến đổi giữa tổng và tích các giá trị lượng giác</t>
+  </si>
+  <si>
+    <t>Tìm tập xác định của hàm số lượng giác</t>
+  </si>
+  <si>
+    <t>Tìm tập giá trị, giá trị lớn nhất và nhỏ nhất của hàm số lượng giác</t>
+  </si>
+  <si>
+    <t>Xét tính chẵn lẻ và tính tuần hoàn của hàm số lượng giác</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế mô tả bằng hàm số lượng giác</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhiều tính chất của một hàm số lượng giác</t>
+  </si>
+  <si>
+    <t>Nhận dạng đồ thị của hàm số lượng giác</t>
+  </si>
+  <si>
+    <t>Giải phương trình sin x = m</t>
+  </si>
+  <si>
+    <t>Giải phương trình cos x = m</t>
+  </si>
+  <si>
+    <t>Giải phương trình tan x = m hoặc cot x = m</t>
+  </si>
+  <si>
+    <t>Tìm nghiệm thoả mãn điều kiện cho trước trên một khoảng</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế đưa về phương trình lượng giác</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhiều tính chất trong một bài toán lượng giác tổng hợp</t>
+  </si>
+  <si>
+    <t>Chương 2. Dãy số. Cấp số cộng và cấp số nhân</t>
+  </si>
+  <si>
+    <t>Tìm số hạng của dãy số cho bởi công thức hoặc hệ thức truy hồi</t>
+  </si>
+  <si>
+    <t>Xét tính tăng, giảm và tính bị chặn của dãy số</t>
+  </si>
+  <si>
+    <t>Tìm công sai của cấp số cộng</t>
+  </si>
+  <si>
+    <t>Tìm số hạng đầu, hoặc tìm đồng thời số hạng đầu và công sai</t>
+  </si>
+  <si>
+    <t>Tìm một số hạng cụ thể hoặc số hạng tổng quát</t>
+  </si>
+  <si>
+    <t>Tính tổng n số hạng đầu của cấp số cộng</t>
+  </si>
+  <si>
+    <t>Nhận biết một dãy số có phải là cấp số cộng</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế bằng cấp số cộng</t>
+  </si>
+  <si>
+    <t>Tìm công bội của cấp số nhân</t>
+  </si>
+  <si>
+    <t>Tìm số hạng đầu, hoặc tìm đồng thời số hạng đầu và công bội</t>
+  </si>
+  <si>
+    <t>Tính tổng n số hạng đầu của cấp số nhân</t>
+  </si>
+  <si>
+    <t>Nhận biết một dãy số có phải là cấp số nhân</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế bằng cấp số nhân</t>
+  </si>
+  <si>
+    <t>Chương 3. Các số đặc trưng đo xu thế trung tâm của mẫu số liệu ghép nhóm</t>
+  </si>
+  <si>
+    <t>Tính số trung bình của mẫu số liệu ghép nhóm</t>
+  </si>
+  <si>
+    <t>Tìm mốt của mẫu số liệu ghép nhóm</t>
+  </si>
+  <si>
+    <t>Lập hoặc đọc bảng tần số ghép nhóm</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế về số trung bình hoặc mốt</t>
+  </si>
+  <si>
+    <t>Tính trung vị của mẫu số liệu ghép nhóm</t>
+  </si>
+  <si>
+    <t>Tính tứ phân vị của mẫu số liệu ghép nhóm</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế về trung vị hoặc tứ phân vị</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhiều tính chất của một mẫu số liệu ghép nhóm</t>
+  </si>
+  <si>
+    <t>Chương 4. Quan hệ song song trong không gian</t>
+  </si>
+  <si>
+    <t>Tìm giao tuyến của hai mặt phẳng hoặc giao điểm của đường thẳng với mặt phẳng</t>
+  </si>
+  <si>
+    <t>Chứng minh thẳng hàng, đồng quy hoặc tính tỉ số trong không gian</t>
+  </si>
+  <si>
+    <t>Xét vị trí tương đối hoặc trả lời câu hỏi lý thuyết về quan hệ trong không gian</t>
+  </si>
+  <si>
+    <t>Chứng minh hai đường thẳng song song trong không gian</t>
+  </si>
+  <si>
+    <t>Chứng minh đường thẳng song song với mặt phẳng</t>
+  </si>
+  <si>
+    <t>Chứng minh hai mặt phẳng song song hoặc dùng định lí Thales trong không gian</t>
+  </si>
+  <si>
+    <t>Vẽ và đọc hình biểu diễn qua phép chiếu song song</t>
+  </si>
+  <si>
+    <t>Chương 5. Giới hạn. Hàm số liên tục</t>
+  </si>
+  <si>
+    <t>Tính giới hạn của dãy số</t>
+  </si>
+  <si>
+    <t>Tính tổng của cấp số nhân lùi vô hạn</t>
+  </si>
+  <si>
+    <t>Tính giới hạn của hàm số</t>
+  </si>
+  <si>
+    <t>Tìm tham số để hàm số có giới hạn theo yêu cầu</t>
+  </si>
+  <si>
+    <t>Xét tính liên tục của hàm số tại một điểm</t>
+  </si>
+  <si>
+    <t>Xét tính liên tục trên một khoảng, đoạn, hoặc đồng thời tại điểm và trên khoảng</t>
+  </si>
+  <si>
+    <t>Chương 6. Hàm số mũ và hàm số logarit</t>
+  </si>
+  <si>
+    <t>Tính giá trị biểu thức chứa luỹ thừa</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế về luỹ thừa</t>
+  </si>
+  <si>
+    <t>Tìm tập xác định của hàm số luỹ thừa</t>
+  </si>
+  <si>
+    <t>Tính giá trị của một biểu thức logarit</t>
+  </si>
+  <si>
+    <t>Rút gọn hoặc biến đổi biểu thức logarit</t>
+  </si>
+  <si>
+    <t>Biểu diễn một logarit theo các logarit đã cho</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế về logarit</t>
+  </si>
+  <si>
+    <t>Tìm tập xác định của hàm số logarit</t>
+  </si>
+  <si>
+    <t>Nhận dạng đồ thị hàm số mũ hoặc hàm số logarit</t>
+  </si>
+  <si>
+    <t>Tìm tập xác định của hàm số mũ, hàm số logarit</t>
+  </si>
+  <si>
+    <t>So sánh các biểu thức chứa luỹ thừa hoặc logarit</t>
+  </si>
+  <si>
+    <t>Giải bài toán lãi suất kép</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế về tăng trưởng hoặc phân rã</t>
+  </si>
+  <si>
+    <t>Xét tính đơn điệu của hàm số mũ hoặc hàm số logarit</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhiều tính chất của một hàm số mũ hoặc logarit</t>
+  </si>
+  <si>
+    <t>Giải bài toán kết hợp hàm mũ, logarit với kiến thức khác</t>
+  </si>
+  <si>
+    <t>Giải phương trình mũ</t>
+  </si>
+  <si>
+    <t>Giải phương trình logarit</t>
+  </si>
+  <si>
+    <t>Giải bất phương trình mũ</t>
+  </si>
+  <si>
+    <t>Giải bất phương trình logarit</t>
+  </si>
+  <si>
+    <t>Tìm tham số hoặc đếm số nghiệm nguyên thoả điều kiện</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhiều tính chất trong một bài toán mũ - logarit tổng hợp</t>
+  </si>
+  <si>
+    <t>Chương 7. Quan hệ vuông góc trong không gian</t>
+  </si>
+  <si>
+    <t>Chứng minh hai đường thẳng vuông góc</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhiều tính chất về quan hệ vuông góc của hai đường thẳng</t>
+  </si>
+  <si>
+    <t>Chứng minh đường thẳng vuông góc với mặt phẳng</t>
+  </si>
+  <si>
+    <t>Xác định chân đường cao hoặc hình chiếu vuông góc</t>
+  </si>
+  <si>
+    <t>Trả lời câu hỏi lý thuyết về quan hệ vuông góc</t>
+  </si>
+  <si>
+    <t>Tính góc giữa đường thẳng và mặt phẳng trong hình chóp</t>
+  </si>
+  <si>
+    <t>Tính góc giữa đường thẳng và mặt phẳng trong lăng trụ hoặc hình hộp</t>
+  </si>
+  <si>
+    <t>Xác định hình chiếu vuông góc của đường thẳng lên mặt phẳng</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế về góc hoặc khoảng cách trong không gian</t>
+  </si>
+  <si>
+    <t>Chứng minh hai mặt phẳng vuông góc</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhiều tính chất trong một bài toán hai mặt phẳng vuông góc</t>
+  </si>
+  <si>
+    <t>Tính khoảng cách từ một điểm đến một mặt phẳng</t>
+  </si>
+  <si>
+    <t>Tính khoảng cách giữa hai đường thẳng chéo nhau</t>
+  </si>
+  <si>
+    <t>Tính khoảng cách từ điểm đến đường thẳng hoặc giữa hai đối tượng song song</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế về khoảng cách</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhiều tính chất trong một bài toán khoảng cách</t>
+  </si>
+  <si>
+    <t>Tính thể tích khối chóp</t>
+  </si>
+  <si>
+    <t>Tính thể tích khối lăng trụ hoặc hình hộp</t>
+  </si>
+  <si>
+    <t>Tính thể tích khối chóp cụt hoặc lăng trụ cụt</t>
+  </si>
+  <si>
+    <t>Tính tỉ số thể tích của hai khối</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế về thể tích</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhiều tính chất trong một bài toán thể tích tổng hợp</t>
+  </si>
+  <si>
+    <t>Tính độ dài đoạn thẳng hoặc yếu tố khác của khối đa diện</t>
+  </si>
+  <si>
+    <t>Nhận biết đặc điểm của hình đa diện (số mặt, số cạnh, số đỉnh)</t>
+  </si>
+  <si>
+    <t>Chương 8. Các quy tắc tính xác suất</t>
+  </si>
+  <si>
+    <t>Nhận biết và mô tả biến cố hợp, biến cố giao, biến cố độc lập</t>
+  </si>
+  <si>
+    <t>Tính xác suất bằng công thức cộng</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế bằng công thức cộng xác suất</t>
+  </si>
+  <si>
+    <t>Tính xác suất bằng công thức nhân cho hai biến cố độc lập</t>
+  </si>
+  <si>
+    <t>Tính xác suất của biến cố đối hoặc biến cố "có ít nhất một"</t>
+  </si>
+  <si>
+    <t>Giải bài toán thực tế bằng công thức nhân xác suất</t>
+  </si>
+  <si>
+    <t>Chương 9. Đạo hàm</t>
+  </si>
+  <si>
+    <t>Tính đạo hàm bằng định nghĩa và nêu ý nghĩa của đạo hàm</t>
+  </si>
+  <si>
+    <t>Tính đạo hàm bằng các quy tắc</t>
+  </si>
+  <si>
+    <t>Viết phương trình tiếp tuyến của đồ thị hàm số</t>
+  </si>
+  <si>
+    <t>Dùng ý nghĩa vật lí của đạo hàm để tính vận tốc, gia tốc</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhiều tính chất trong một bài toán đạo hàm tổng hợp</t>
+  </si>
+  <si>
+    <t>Tính đạo hàm cấp hai và nêu ý nghĩa vật lí của nó</t>
   </si>
 </sst>
 </file>
@@ -590,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -601,7 +952,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -936,14 +1292,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7BC53D4-DA32-46F8-8217-5D3B03E35241}">
-  <dimension ref="A1:C147"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C259"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="76.5" customWidth="1"/>
     <col min="3" max="3" width="61" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -954,7 +1310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>12</v>
       </c>
@@ -965,7 +1321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>12</v>
       </c>
@@ -976,7 +1332,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>12</v>
       </c>
@@ -987,7 +1343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>12</v>
       </c>
@@ -998,7 +1354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>12</v>
       </c>
@@ -1009,7 +1365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>12</v>
       </c>
@@ -1020,7 +1376,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>12</v>
       </c>
@@ -1031,7 +1387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>12</v>
       </c>
@@ -1042,7 +1398,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>12</v>
       </c>
@@ -1053,7 +1409,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>12</v>
       </c>
@@ -1064,7 +1420,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -1075,7 +1431,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1086,7 +1442,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1097,7 +1453,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -1108,7 +1464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -1119,7 +1475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>12</v>
       </c>
@@ -1130,7 +1486,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>12</v>
       </c>
@@ -1141,7 +1497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>12</v>
       </c>
@@ -1152,7 +1508,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>12</v>
       </c>
@@ -1163,7 +1519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>12</v>
       </c>
@@ -1174,7 +1530,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>12</v>
       </c>
@@ -1185,7 +1541,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>12</v>
       </c>
@@ -1196,7 +1552,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>12</v>
       </c>
@@ -1207,7 +1563,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>12</v>
       </c>
@@ -1218,7 +1574,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>12</v>
       </c>
@@ -1229,7 +1585,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>12</v>
       </c>
@@ -1240,7 +1596,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>12</v>
       </c>
@@ -1251,7 +1607,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>12</v>
       </c>
@@ -1262,7 +1618,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>12</v>
       </c>
@@ -1273,7 +1629,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>12</v>
       </c>
@@ -1284,7 +1640,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>12</v>
       </c>
@@ -1295,7 +1651,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>12</v>
       </c>
@@ -1306,7 +1662,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>12</v>
       </c>
@@ -1317,7 +1673,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>12</v>
       </c>
@@ -1328,7 +1684,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>12</v>
       </c>
@@ -1339,7 +1695,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>12</v>
       </c>
@@ -1350,7 +1706,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>12</v>
       </c>
@@ -1361,7 +1717,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>12</v>
       </c>
@@ -1372,7 +1728,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>12</v>
       </c>
@@ -1383,7 +1739,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>12</v>
       </c>
@@ -1394,7 +1750,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>12</v>
       </c>
@@ -1405,7 +1761,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>12</v>
       </c>
@@ -1416,7 +1772,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>12</v>
       </c>
@@ -1427,7 +1783,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>12</v>
       </c>
@@ -1438,7 +1794,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>12</v>
       </c>
@@ -1449,7 +1805,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>12</v>
       </c>
@@ -1460,7 +1816,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>12</v>
       </c>
@@ -1471,7 +1827,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>12</v>
       </c>
@@ -1482,7 +1838,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>12</v>
       </c>
@@ -1493,7 +1849,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>12</v>
       </c>
@@ -1504,7 +1860,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>12</v>
       </c>
@@ -1515,7 +1871,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>12</v>
       </c>
@@ -1526,7 +1882,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>12</v>
       </c>
@@ -1537,7 +1893,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>12</v>
       </c>
@@ -1548,7 +1904,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>12</v>
       </c>
@@ -1559,7 +1915,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>12</v>
       </c>
@@ -1570,7 +1926,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>12</v>
       </c>
@@ -1581,7 +1937,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>12</v>
       </c>
@@ -1592,7 +1948,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>12</v>
       </c>
@@ -1603,7 +1959,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>12</v>
       </c>
@@ -1614,7 +1970,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>12</v>
       </c>
@@ -1625,7 +1981,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>12</v>
       </c>
@@ -1636,7 +1992,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>12</v>
       </c>
@@ -1647,7 +2003,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>12</v>
       </c>
@@ -1658,7 +2014,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>12</v>
       </c>
@@ -1669,7 +2025,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>12</v>
       </c>
@@ -1680,7 +2036,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>12</v>
       </c>
@@ -1691,7 +2047,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>12</v>
       </c>
@@ -1702,7 +2058,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>12</v>
       </c>
@@ -1713,7 +2069,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>12</v>
       </c>
@@ -1724,7 +2080,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>12</v>
       </c>
@@ -1735,7 +2091,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>12</v>
       </c>
@@ -1746,7 +2102,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>12</v>
       </c>
@@ -1757,7 +2113,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>12</v>
       </c>
@@ -1768,7 +2124,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>12</v>
       </c>
@@ -1779,7 +2135,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>12</v>
       </c>
@@ -1790,7 +2146,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>12</v>
       </c>
@@ -1801,7 +2157,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>12</v>
       </c>
@@ -1812,7 +2168,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>12</v>
       </c>
@@ -1823,7 +2179,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>12</v>
       </c>
@@ -1834,7 +2190,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>12</v>
       </c>
@@ -1845,7 +2201,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>12</v>
       </c>
@@ -1856,7 +2212,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>12</v>
       </c>
@@ -1867,7 +2223,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>12</v>
       </c>
@@ -1878,7 +2234,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>12</v>
       </c>
@@ -1889,7 +2245,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>12</v>
       </c>
@@ -1900,7 +2256,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>12</v>
       </c>
@@ -1911,7 +2267,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>12</v>
       </c>
@@ -1922,7 +2278,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>12</v>
       </c>
@@ -1933,7 +2289,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>12</v>
       </c>
@@ -1944,7 +2300,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>12</v>
       </c>
@@ -1955,7 +2311,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>12</v>
       </c>
@@ -1966,7 +2322,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>12</v>
       </c>
@@ -1977,7 +2333,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>12</v>
       </c>
@@ -1988,7 +2344,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>12</v>
       </c>
@@ -1999,7 +2355,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>12</v>
       </c>
@@ -2010,7 +2366,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>12</v>
       </c>
@@ -2021,7 +2377,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>12</v>
       </c>
@@ -2032,7 +2388,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>12</v>
       </c>
@@ -2043,7 +2399,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>12</v>
       </c>
@@ -2054,7 +2410,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>12</v>
       </c>
@@ -2065,7 +2421,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>12</v>
       </c>
@@ -2076,7 +2432,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>12</v>
       </c>
@@ -2087,7 +2443,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>12</v>
       </c>
@@ -2098,7 +2454,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>12</v>
       </c>
@@ -2109,7 +2465,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>12</v>
       </c>
@@ -2120,7 +2476,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>12</v>
       </c>
@@ -2131,7 +2487,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>12</v>
       </c>
@@ -2142,7 +2498,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>12</v>
       </c>
@@ -2153,7 +2509,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>12</v>
       </c>
@@ -2164,7 +2520,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>12</v>
       </c>
@@ -2175,7 +2531,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>12</v>
       </c>
@@ -2186,7 +2542,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>12</v>
       </c>
@@ -2197,7 +2553,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>12</v>
       </c>
@@ -2208,7 +2564,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>12</v>
       </c>
@@ -2219,7 +2575,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>12</v>
       </c>
@@ -2230,7 +2586,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>12</v>
       </c>
@@ -2241,7 +2597,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>12</v>
       </c>
@@ -2252,7 +2608,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>12</v>
       </c>
@@ -2263,7 +2619,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>12</v>
       </c>
@@ -2274,7 +2630,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>12</v>
       </c>
@@ -2285,7 +2641,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>12</v>
       </c>
@@ -2296,7 +2652,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>12</v>
       </c>
@@ -2307,7 +2663,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>12</v>
       </c>
@@ -2318,7 +2674,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>12</v>
       </c>
@@ -2329,7 +2685,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>12</v>
       </c>
@@ -2340,7 +2696,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>12</v>
       </c>
@@ -2351,7 +2707,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>12</v>
       </c>
@@ -2362,7 +2718,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>12</v>
       </c>
@@ -2373,7 +2729,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>12</v>
       </c>
@@ -2384,7 +2740,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>12</v>
       </c>
@@ -2395,7 +2751,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>12</v>
       </c>
@@ -2406,7 +2762,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>12</v>
       </c>
@@ -2417,7 +2773,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>12</v>
       </c>
@@ -2428,7 +2784,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>12</v>
       </c>
@@ -2439,7 +2795,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>12</v>
       </c>
@@ -2450,7 +2806,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>12</v>
       </c>
@@ -2461,7 +2817,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>12</v>
       </c>
@@ -2472,7 +2828,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>12</v>
       </c>
@@ -2483,7 +2839,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>12</v>
       </c>
@@ -2494,7 +2850,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>12</v>
       </c>
@@ -2505,7 +2861,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>12</v>
       </c>
@@ -2516,7 +2872,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>12</v>
       </c>
@@ -2527,7 +2883,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>12</v>
       </c>
@@ -2538,7 +2894,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>12</v>
       </c>
@@ -2549,7 +2905,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3">
         <v>12</v>
       </c>
@@ -2558,6 +2914,1238 @@
       </c>
       <c r="C147" s="4" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="5">
+        <v>11</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="5">
+        <v>11</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="5">
+        <v>11</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="5">
+        <v>11</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="5">
+        <v>11</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="5">
+        <v>11</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="5">
+        <v>11</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="5">
+        <v>11</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="5">
+        <v>11</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="5">
+        <v>11</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="5">
+        <v>11</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="5">
+        <v>11</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="5">
+        <v>11</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="5">
+        <v>11</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="5">
+        <v>11</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="5">
+        <v>11</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="5">
+        <v>11</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="5">
+        <v>11</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="5">
+        <v>11</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="5">
+        <v>11</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="5">
+        <v>11</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="5">
+        <v>11</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="5">
+        <v>11</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="5">
+        <v>11</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="5">
+        <v>11</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="5">
+        <v>11</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="5">
+        <v>11</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="5">
+        <v>11</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="5">
+        <v>11</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="5">
+        <v>11</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="5">
+        <v>11</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="5">
+        <v>11</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="5">
+        <v>11</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="5">
+        <v>11</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="5">
+        <v>11</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="5">
+        <v>11</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="5">
+        <v>11</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="5">
+        <v>11</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="5">
+        <v>11</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A187" s="5">
+        <v>11</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A188" s="5">
+        <v>11</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="5">
+        <v>11</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="5">
+        <v>11</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="5">
+        <v>11</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A192" s="5">
+        <v>11</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="5">
+        <v>11</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A194" s="5">
+        <v>11</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="5">
+        <v>11</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="5">
+        <v>11</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A197" s="5">
+        <v>11</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A198" s="5">
+        <v>11</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A199" s="5">
+        <v>11</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A200" s="5">
+        <v>11</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A201" s="5">
+        <v>11</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A202" s="5">
+        <v>11</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="5">
+        <v>11</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A204" s="5">
+        <v>11</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A205" s="5">
+        <v>11</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A206" s="5">
+        <v>11</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A207" s="5">
+        <v>11</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A208" s="5">
+        <v>11</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A209" s="5">
+        <v>11</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A210" s="5">
+        <v>11</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A211" s="5">
+        <v>11</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A212" s="5">
+        <v>11</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A213" s="5">
+        <v>11</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A214" s="5">
+        <v>11</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A215" s="5">
+        <v>11</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A216" s="5">
+        <v>11</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A217" s="5">
+        <v>11</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A218" s="5">
+        <v>11</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A219" s="5">
+        <v>11</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A220" s="5">
+        <v>11</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A221" s="5">
+        <v>11</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A222" s="5">
+        <v>11</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A223" s="5">
+        <v>11</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A224" s="5">
+        <v>11</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A225" s="5">
+        <v>11</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A226" s="5">
+        <v>11</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A227" s="5">
+        <v>11</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A228" s="5">
+        <v>11</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A229" s="5">
+        <v>11</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A230" s="5">
+        <v>11</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A231" s="5">
+        <v>11</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A232" s="5">
+        <v>11</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A233" s="5">
+        <v>11</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A234" s="5">
+        <v>11</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A235" s="5">
+        <v>11</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A236" s="5">
+        <v>11</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A237" s="5">
+        <v>11</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A238" s="5">
+        <v>11</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A239" s="5">
+        <v>11</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A240" s="5">
+        <v>11</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A241" s="5">
+        <v>11</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A242" s="5">
+        <v>11</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A243" s="5">
+        <v>11</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="5">
+        <v>11</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A245" s="5">
+        <v>11</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A246" s="5">
+        <v>11</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A247" s="5">
+        <v>11</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A248" s="5">
+        <v>11</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A249" s="5">
+        <v>11</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A250" s="5">
+        <v>11</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A251" s="5">
+        <v>11</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A252" s="5">
+        <v>11</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A253" s="5">
+        <v>11</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A254" s="5">
+        <v>11</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A255" s="5">
+        <v>11</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A256" s="5">
+        <v>11</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A257" s="5">
+        <v>11</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A258" s="5">
+        <v>11</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A259" s="5">
+        <v>11</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
